--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:42:43+00:00</t>
+    <t>2026-06-22T14:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:38:01+00:00</t>
+    <t>2026-06-29T12:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:42:10+00:00</t>
+    <t>2026-07-07T09:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T09:34:50+00:00</t>
+    <t>2026-07-16T11:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:52:18+00:00</t>
+    <t>2026-07-16T13:43:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T13:43:45+00:00</t>
+    <t>2026-07-16T16:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:12:39+00:00</t>
+    <t>2026-07-20T14:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:23:22+00:00</t>
+    <t>2026-08-12T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:16:17+00:00</t>
+    <t>2026-08-13T08:08:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:08:00+00:00</t>
+    <t>2026-08-13T08:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,6 +116,9 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R13-CommuneOM/FHIR/TRE-R13-CommuneOM</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R20-Pays/FHIR/TRE-R20-Pays</t>
   </si>
 </sst>
 </file>
@@ -422,4 +426,44 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:33:40+00:00</t>
+    <t>2026-08-13T08:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:58:16+00:00</t>
+    <t>2026-08-13T09:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:15:12+00:00</t>
+    <t>2026-08-13T09:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:41:50+00:00</t>
+    <t>2026-08-13T12:00:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-insee-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:00:16+00:00</t>
+    <t>2026-08-13T12:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
